--- a/aq_files/0676.xlsx
+++ b/aq_files/0676.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dictionary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,468 +413,573 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Question</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Question</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Details</t>
-        </is>
-      </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Difficulty</t>
+          <t>Options (if MCQ)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Question Type</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MCQ</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Dictionary stores:</t>
+          <t>YAML stands for __________.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>A) key-value B) list C) set D) tuple</t>
+          <t>One word</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MCQ</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Keys must be:</t>
+          <t>How do you represent a comment in YAML?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>A) immutable B) mutable C) both D) none</t>
+          <t>One word</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MCQ</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Values can be:</t>
+          <t>Convert this JSON to YAML: {"name": "John", "age": 30}</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>A) any type B) only int C) only str D) none</t>
+          <t>Write YAML</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Coding</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MCQ</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>dict is ordered?</t>
+          <t>In YAML, lists are represented with a __________ followed by space.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>A) Yes (3.7+) B) No C) maybe D) none</t>
+          <t>One word</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Coding</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Count frequency of elements.</t>
+          <t>How do you represent a multi-line string in YAML?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>LeetCode-style problem</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>A) | B) &gt; C) both A and B D) \</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Coding</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Find first non-repeating char.</t>
+          <t>What does null or ~ represent in YAML?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>LeetCode-style problem</t>
+          <t>One word</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Coding</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Group anagrams.</t>
+          <t>Scenario: Write YAML for a list of fruits: apple, banana, orange.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>LeetCode-style problem</t>
+          <t>Scenario</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Coding</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Two sum using dictionary.</t>
+          <t>YAML uses __________ spaces for indentation (not tabs).</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>LeetCode-style problem</t>
+          <t>One word</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Coding</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Merge dictionaries.</t>
+          <t>True or False: YAML is a superset of JSON.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>LeetCode-style problem</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>A) True B) False</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Coding</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Sort dictionary by value.</t>
+          <t>Which character separates key-value pairs in YAML?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>LeetCode-style problem</t>
+          <t>One word</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Write a YAML dictionary with key "server" having values port=8080 and ssl=true.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Write YAML</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>Coding</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Find key with max value.</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>LeetCode-style problem</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Coding</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Invert dictionary.</t>
+          <t>What does &gt; do in YAML?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>LeetCode-style problem</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>A) Folded block scalar B) Literal block C) Comment D) List</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Coding</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Check key existence.</t>
+          <t>How do you represent boolean True in YAML?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>LeetCode-style problem</t>
+          <t>One word</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Coding</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Delete key from dictionary.</t>
+          <t>Scenario: Write YAML for an array of objects: [{name: a, val:1}, {name:b, val:2}]</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>LeetCode-style problem</t>
+          <t>Scenario</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Coding</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Nested dictionary traversal.</t>
+          <t>What is the correct way to write a dictionary inside a dictionary in YAML?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>LeetCode-style problem</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>A) key:{sub:val} B) key:\n sub: val C) both D) key=sub:val</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Coding</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Word count in sentence.</t>
+          <t>Which file extension is NOT used for YAML?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>LeetCode-style problem</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>A) .yaml B) .yml C) .yamlml D) both A and B are valid</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Coding</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Find duplicate keys.</t>
+          <t>What does | do in YAML?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>LeetCode-style problem</t>
+          <t>One word</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Coding</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Combine two dictionaries.</t>
+          <t>Scenario: You have a string "Line1\nLine2\nLine3" that should preserve newlines. Which YAML syntax?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>LeetCode-style problem</t>
+          <t>Scenario</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Coding</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Find intersection of dict keys.</t>
+          <t>True or False: In YAML, yes and no are interpreted as booleans.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>LeetCode-style problem</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>A) True B) False</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Write YAML anchor and alias for reusing value "John".</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Write YAML</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>Coding</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>LRU cache basic logic.</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>LeetCode-style problem</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Hard</t>
         </is>
       </c>
     </row>
